--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_UDO.xlsx
@@ -13,10 +13,10 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -421,11 +421,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,24 +472,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M. Morgan (14.5 ppg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>M. Morgan (28.3 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G. Powell (30.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>best_duo</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>J. Turner | S. Victo (6.6 net)</t>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Turner | M. Morgan (-12.3 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>best_trio</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J. Aramburu | M. Morgan | P. Nixon (-25.2 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -496,28 +548,615 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="38" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>M. Morgan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>46.0%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Turner</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>54</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>50.7%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-48.3</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>P. Nixon</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>32.1%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>35.7%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>44.2%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-29.9</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Aramburu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>51.2%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C. Rodger</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>54.9%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>G. Powell</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>56.7%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>61.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>efficient, impact</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -560,13 +1199,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -645,26 +1284,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>J. Turner | S. Victo</t>
+          <t>J. Turner | M. Morgan</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>18.2</v>
+        <v>35.9</v>
       </c>
       <c r="H2" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="I2" t="n">
-        <v>72.7</v>
+        <v>91.5</v>
       </c>
       <c r="J2" t="n">
-        <v>6.6</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="3">
@@ -689,22 +1328,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G3" t="n">
-        <v>16.3</v>
+        <v>30.6</v>
       </c>
       <c r="H3" t="n">
-        <v>112.7</v>
+        <v>90.2</v>
       </c>
       <c r="I3" t="n">
-        <v>78.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="J3" t="n">
-        <v>34.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
@@ -725,30 +1364,150 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>J. Turner | S. Victo</t>
+          <t>J. Aramburu | M. Morgan</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
+        <v>19</v>
+      </c>
+      <c r="G4" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>J. Aramburu | M. Morgan | P. Nixon</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-25.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C. Rodger | M. Morgan | P. Nixon</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
         <v>9</v>
       </c>
-      <c r="G4" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="I4" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6.6</v>
+      <c r="G6" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>73</v>
+      </c>
+      <c r="I6" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-10.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>C. Rodger | M. Morgan | P. Nixon</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>73</v>
+      </c>
+      <c r="I7" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-10.4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:J7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_UDO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_UDO.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -425,7 +425,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Morgan (14.5 ppg)</t>
+          <t>P. Nixon (16.3 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M. Morgan (28.3 mpg)</t>
+          <t>M. Morgan (26.6 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G. Powell (30.0%)</t>
+          <t>G. Powell (38.9%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Turner | M. Morgan (-12.3 net)</t>
+          <t>J. Aramburu | M. Morgan (9.7 net)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Aramburu | M. Morgan | P. Nixon (-25.2 net)</t>
+          <t>C. Rodger | J. Turner | P. Nixon (0 net)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>56.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>28.3</v>
+        <v>26.6</v>
       </c>
       <c r="H2" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -744,19 +744,19 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-1</v>
+        <v>7.7</v>
       </c>
       <c r="T2" t="n">
-        <v>29.7</v>
+        <v>31</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -777,28 +777,28 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>24.7</v>
       </c>
       <c r="H3" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -808,12 +808,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -823,23 +823,23 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-14.5</v>
+        <v>-3</v>
       </c>
       <c r="T3" t="n">
-        <v>-48.3</v>
+        <v>-23.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes</t>
+          <t>high-minutes, efficient</t>
         </is>
       </c>
     </row>
@@ -856,69 +856,69 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>48.7</v>
+        <v>71</v>
       </c>
       <c r="G4" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="H4" t="n">
-        <v>14.5</v>
+        <v>16.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-12</v>
+        <v>2</v>
       </c>
       <c r="T4" t="n">
-        <v>-29.9</v>
+        <v>5.9</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer</t>
+          <t>primary-scorer, impact</t>
         </is>
       </c>
     </row>
@@ -935,69 +935,69 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>45.7</v>
+        <v>69</v>
       </c>
       <c r="G5" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-10.5</v>
+        <v>-1.7</v>
       </c>
       <c r="T5" t="n">
-        <v>-18.1</v>
+        <v>-9</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>rotation</t>
+          <t>efficient</t>
         </is>
       </c>
     </row>
@@ -1014,22 +1014,22 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>42.6</v>
+        <v>64.3</v>
       </c>
       <c r="G6" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>6.3</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1038,14 +1038,14 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>6.3</v>
       </c>
       <c r="T6" t="n">
-        <v>15.1</v>
+        <v>15.7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>primary-scorer, impact</t>
         </is>
       </c>
     </row>
@@ -1089,74 +1089,240 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>40.7</v>
+        <v>61.6</v>
       </c>
       <c r="G7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>-2</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>efficient, impact</t>
+          <t>primary-scorer, efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S. Victo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>61.8%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>57.3%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UD Oliveirense</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>T. Dias</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>28.4%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U7"/>
+  <autoFilter ref="A1:U9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1205,7 +1371,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1284,26 +1450,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>J. Turner | M. Morgan</t>
+          <t>J. Aramburu | M. Morgan</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="G2" t="n">
-        <v>35.9</v>
+        <v>53.5</v>
       </c>
       <c r="H2" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="I2" t="n">
         <v>79.2</v>
       </c>
-      <c r="I2" t="n">
-        <v>91.5</v>
-      </c>
       <c r="J2" t="n">
-        <v>-12.3</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -1324,26 +1490,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C. Rodger | M. Morgan</t>
+          <t>M. Morgan | P. Nixon</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>30.6</v>
+        <v>44.4</v>
       </c>
       <c r="H3" t="n">
-        <v>90.2</v>
+        <v>86.5</v>
       </c>
       <c r="I3" t="n">
-        <v>86.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="4">
@@ -1364,26 +1530,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>J. Aramburu | M. Morgan</t>
+          <t>M. Morgan | P. Nixon</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>34.7</v>
+        <v>44.4</v>
       </c>
       <c r="H4" t="n">
-        <v>81.8</v>
+        <v>86.5</v>
       </c>
       <c r="I4" t="n">
-        <v>84.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.3</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="5">
@@ -1404,26 +1570,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>J. Aramburu | M. Morgan | P. Nixon</t>
+          <t>C. Rodger | J. Turner | P. Nixon</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>20.6</v>
+        <v>28.1</v>
       </c>
       <c r="H5" t="n">
-        <v>68</v>
+        <v>98.2</v>
       </c>
       <c r="I5" t="n">
-        <v>93.2</v>
+        <v>98.2</v>
       </c>
       <c r="J5" t="n">
-        <v>-25.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1444,26 +1610,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C. Rodger | M. Morgan | P. Nixon</t>
+          <t>G. Powell | J. Aramburu | M. Morgan</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>19.2</v>
+        <v>24.4</v>
       </c>
       <c r="H6" t="n">
-        <v>73</v>
+        <v>103.2</v>
       </c>
       <c r="I6" t="n">
-        <v>83.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.4</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="7">
@@ -1484,26 +1650,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>C. Rodger | M. Morgan | P. Nixon</t>
+          <t>G. Powell | J. Aramburu | M. Morgan</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G7" t="n">
-        <v>19.2</v>
+        <v>24.4</v>
       </c>
       <c r="H7" t="n">
-        <v>73</v>
+        <v>103.2</v>
       </c>
       <c r="I7" t="n">
-        <v>83.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="J7" t="n">
-        <v>-10.4</v>
+        <v>34.4</v>
       </c>
     </row>
   </sheetData>
